--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
@@ -19,7 +19,7 @@
     <t>Internal Audit Report</t>
   </si>
   <si>
-    <t>AUD-2026-09 — Payments incident investigation</t>
+    <t>AUD-2026-03 — Business Continuity Readiness</t>
   </si>
   <si>
     <t>Organisation</t>
@@ -46,7 +46,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-16 17:58 UTC</t>
+    <t>2026-08-17 15:43 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -61,19 +61,19 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>AUD-2026-09</t>
+    <t>AUD-2026-03</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Payments incident investigation</t>
+    <t>Business Continuity Readiness</t>
   </si>
   <si>
     <t>Lead auditor</t>
   </si>
   <si>
-    <t>Mehdi Tantaoui</t>
+    <t>Mahmoud Abdulaziz</t>
   </si>
   <si>
     <t>Status</t>
@@ -82,19 +82,19 @@
     <t>Objective</t>
   </si>
   <si>
-    <t>Establish what happened.</t>
+    <t>Assess ICT continuity and recovery testing.</t>
   </si>
   <si>
     <t>Scope</t>
   </si>
   <si>
-    <t>Outbound payments, Jan–Feb.</t>
+    <t>Backup, restoration testing, RTO/RPO adherence.</t>
   </si>
   <si>
     <t>Criteria</t>
   </si>
   <si>
-    <t>ISO 27001 A.8.16</t>
+    <t>ISO 27001 A.5.30</t>
   </si>
   <si>
     <t>Conclusion</t>
